--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756569</v>
+        <v>131756438</v>
       </c>
       <c r="B8" t="n">
         <v>79261</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774602</v>
+        <v>774568</v>
       </c>
       <c r="R8" t="n">
-        <v>7122207</v>
+        <v>7122253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131756438</v>
+        <v>131756259</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,30 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774568</v>
+        <v>774672</v>
       </c>
       <c r="R9" t="n">
-        <v>7122253</v>
+        <v>7122139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,13 +1497,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131756259</v>
+        <v>131756569</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,31 +1537,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774672</v>
+        <v>774602</v>
       </c>
       <c r="R10" t="n">
-        <v>7122139</v>
+        <v>7122207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,17 +1606,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131756327</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131756639</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131756693</v>
+        <v>131756249</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,30 +892,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774586</v>
+        <v>774616</v>
       </c>
       <c r="R4" t="n">
-        <v>7121973</v>
+        <v>7121965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,13 +962,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131756249</v>
+        <v>131756693</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,31 +1002,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774616</v>
+        <v>774586</v>
       </c>
       <c r="R5" t="n">
-        <v>7121965</v>
+        <v>7121973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,17 +1071,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>131756218</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131756313</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756438</v>
+        <v>131756259</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,30 +1322,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774568</v>
+        <v>774672</v>
       </c>
       <c r="R8" t="n">
-        <v>7122253</v>
+        <v>7122139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,13 +1392,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1416,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131756259</v>
+        <v>131756438</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,31 +1432,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1459,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774672</v>
+        <v>774568</v>
       </c>
       <c r="R9" t="n">
-        <v>7122139</v>
+        <v>7122253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,17 +1501,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>131756569</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131756484</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>131756393</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>131756525</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131756656</v>
+        <v>131756412</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,31 +1962,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774621</v>
+        <v>774608</v>
       </c>
       <c r="R14" t="n">
-        <v>7122071</v>
+        <v>7122238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,17 +2031,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131756412</v>
+        <v>131756656</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,30 +2067,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2103,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774608</v>
+        <v>774621</v>
       </c>
       <c r="R15" t="n">
-        <v>7122238</v>
+        <v>7122071</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,13 +2137,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>131756277</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>131756301</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131756306</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131756249</v>
+        <v>131756693</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,31 +892,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -924,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774616</v>
+        <v>774586</v>
       </c>
       <c r="R4" t="n">
-        <v>7121965</v>
+        <v>7121973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +961,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131756693</v>
+        <v>131756249</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,30 +997,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774586</v>
+        <v>774616</v>
       </c>
       <c r="R5" t="n">
-        <v>7121973</v>
+        <v>7121965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,13 +1067,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131756327</v>
+        <v>131756639</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774625</v>
+        <v>774574</v>
       </c>
       <c r="R2" t="n">
-        <v>7122256</v>
+        <v>7122053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131756639</v>
+        <v>131756327</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +791,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774574</v>
+        <v>774625</v>
       </c>
       <c r="R3" t="n">
-        <v>7122053</v>
+        <v>7122256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756259</v>
+        <v>131756569</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,31 +1322,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774672</v>
+        <v>774602</v>
       </c>
       <c r="R8" t="n">
-        <v>7122139</v>
+        <v>7122207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1391,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131756569</v>
+        <v>131756259</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,30 +1532,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774602</v>
+        <v>774672</v>
       </c>
       <c r="R10" t="n">
-        <v>7122207</v>
+        <v>7122139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,13 +1602,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131756639</v>
+        <v>131756327</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>91858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -717,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774574</v>
+        <v>774625</v>
       </c>
       <c r="R2" t="n">
-        <v>7122053</v>
+        <v>7122256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131756327</v>
+        <v>131756639</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,23 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774625</v>
+        <v>774574</v>
       </c>
       <c r="R3" t="n">
-        <v>7122256</v>
+        <v>7122053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
         <v>131756693</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131756249</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>131756218</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131756313</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756569</v>
+        <v>131756259</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,30 +1322,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774602</v>
+        <v>774672</v>
       </c>
       <c r="R8" t="n">
-        <v>7122207</v>
+        <v>7122139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,13 +1392,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1419,7 +1424,7 @@
         <v>131756438</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131756259</v>
+        <v>131756569</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,31 +1537,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774672</v>
+        <v>774602</v>
       </c>
       <c r="R10" t="n">
-        <v>7122139</v>
+        <v>7122207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,17 +1606,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>131756484</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>131756393</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>131756525</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131756412</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>131756656</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>131756277</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>131756301</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131756306</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756259</v>
+        <v>131756438</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,31 +1322,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774672</v>
+        <v>774568</v>
       </c>
       <c r="R8" t="n">
-        <v>7122139</v>
+        <v>7122253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1391,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131756438</v>
+        <v>131756569</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1463,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774568</v>
+        <v>774602</v>
       </c>
       <c r="R9" t="n">
-        <v>7122253</v>
+        <v>7122207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131756569</v>
+        <v>131756259</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,30 +1532,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774602</v>
+        <v>774672</v>
       </c>
       <c r="R10" t="n">
-        <v>7122207</v>
+        <v>7122139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,13 +1602,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131756327</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131756639</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>131756693</v>
       </c>
       <c r="B4" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131756313</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131756438</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>131756569</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131756484</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>131756393</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131756412</v>
       </c>
       <c r="B14" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>131756277</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8477-2026 artfynd.xlsx
+++ b/artfynd/A 8477-2026 artfynd.xlsx
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131756438</v>
+        <v>131756569</v>
       </c>
       <c r="B8" t="n">
         <v>79317</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774568</v>
+        <v>774602</v>
       </c>
       <c r="R8" t="n">
-        <v>7122253</v>
+        <v>7122207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131756569</v>
+        <v>131756259</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,30 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774602</v>
+        <v>774672</v>
       </c>
       <c r="R9" t="n">
-        <v>7122207</v>
+        <v>7122139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,13 +1497,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131756259</v>
+        <v>131756438</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,31 +1537,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774672</v>
+        <v>774568</v>
       </c>
       <c r="R10" t="n">
-        <v>7122139</v>
+        <v>7122253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,17 +1606,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131756412</v>
+        <v>131756656</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,30 +1962,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1993,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774608</v>
+        <v>774621</v>
       </c>
       <c r="R14" t="n">
-        <v>7122238</v>
+        <v>7122071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,13 +2032,17 @@
           <t>2026-02-25</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131756656</v>
+        <v>131756412</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,31 +2072,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774621</v>
+        <v>774608</v>
       </c>
       <c r="R15" t="n">
-        <v>7122071</v>
+        <v>7122238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,17 +2141,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
